--- a/docs/FCC-core-55-70/build47-item-walk-v1-2026-07-29.xlsx
+++ b/docs/FCC-core-55-70/build47-item-walk-v1-2026-07-29.xlsx
@@ -548,7 +548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1414,6 +1414,43 @@
       <c r="H26" s="5" t="inlineStr"/>
       <c r="I26" s="5" t="inlineStr"/>
     </row>
+    <row r="27" ht="88" customHeight="1">
+      <c r="A27" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>One account naming everywhere (your finding #4)</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>The Record-a-transaction picker names accounts its own way — three imported cash accounts render as three identical "E*Trade savings" chips; impossible to tell apart.</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>The picker uses the SAME shared account-naming helper as Net worth and the rest of the app: real holding names, "· 1 / · 2" for true twins. A source pin bans local account-naming.</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Record a transaction (Invest + holding detail)</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>B46 feedback #4</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>NO — approved naming, applied</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr"/>
+      <c r="I27" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A15:I15"/>

--- a/docs/FCC-core-55-70/build47-item-walk-v1-2026-07-29.xlsx
+++ b/docs/FCC-core-55-70/build47-item-walk-v1-2026-07-29.xlsx
@@ -548,7 +548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1451,6 +1451,43 @@
       <c r="H27" s="5" t="inlineStr"/>
       <c r="I27" s="5" t="inlineStr"/>
     </row>
+    <row r="28" ht="80" customHeight="1">
+      <c r="A28" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>Confirm before removing an account (your finding #5)</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>The account editor's Remove button deletes the account the instant you tap it — no confirmation, no undo.</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>A confirm dialog first: "Remove &lt;account&gt;? Its $X leaves your net worth." — same pattern the income sources already use.</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>Net worth account editor</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>B46 feedback #5</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>NO — a standard dialog</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr"/>
+      <c r="I28" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A15:I15"/>

--- a/docs/FCC-core-55-70/build47-item-walk-v1-2026-07-29.xlsx
+++ b/docs/FCC-core-55-70/build47-item-walk-v1-2026-07-29.xlsx
@@ -548,7 +548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1488,6 +1488,80 @@
       <c r="H28" s="5" t="inlineStr"/>
       <c r="I28" s="5" t="inlineStr"/>
     </row>
+    <row r="29" ht="88" customHeight="1">
+      <c r="A29" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>Plain words + a real door on the Income tab (your finding #9a)</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>The note under "＋ Add or set up income" reads: "Opens the steady-or-varies question. Rich editors (equity comp, rental) live in the income manager." — internal jargon, and it points at a screen without taking you there.</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Plain English with a working link: "Asks whether your pay is the same every month or varies. Pay from stock vesting or a rental? They have their own screen — open Income ›" (the link opens the menu's Income screen).</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Cash flow · Income tab</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>B46 feedback #9</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>TINY — words + one link</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr"/>
+      <c r="I29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30" ht="88" customHeight="1">
+      <c r="A30" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>Every income source can be ADDED, not just edited (your finding #9b)</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>On the Income screen, the stock-vesting and rental editors open only from their source rows — which exist only when the amount is already above zero. Skipped them at onboarding → no way in, ever.</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>An "＋ Add an income source" path on the Income screen offering bonus, stock vesting, rental and self-employment — each opening its existing editor. No new editors, just reachable ones.</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>Income screen (menu)</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>B46 feedback #9</t>
+        </is>
+      </c>
+      <c r="G30" s="8" t="inlineStr">
+        <is>
+          <t>TINY — an add row, existing pattern</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr"/>
+      <c r="I30" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A15:I15"/>

--- a/docs/FCC-core-55-70/build47-item-walk-v1-2026-07-29.xlsx
+++ b/docs/FCC-core-55-70/build47-item-walk-v1-2026-07-29.xlsx
@@ -95,7 +95,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -115,6 +115,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -548,7 +551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -560,6 +563,7 @@
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="42" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -608,6 +612,11 @@
           <t>Your comments</t>
         </is>
       </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>Outcome (my status — kept current)</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
@@ -650,8 +659,17 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr"/>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>APPROVE FOR BUILD 47 — given verbally, 2026-07-30 ("Approve all 25")</t>
+        </is>
+      </c>
       <c r="I3" s="5" t="inlineStr"/>
+      <c r="J3" s="9" t="inlineStr">
+        <is>
+          <t>BUILT 2026-07-30 — pinned; suite 1,311 green</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="88" customHeight="1">
       <c r="A4" s="5" t="n">
@@ -687,8 +705,17 @@
           <t>TINY — same approved table</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr"/>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>APPROVE FOR BUILD 47 — given verbally, 2026-07-30 ("Approve all 25")</t>
+        </is>
+      </c>
       <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="9" t="inlineStr">
+        <is>
+          <t>BUILT 2026-07-30 — pinned; suite 1,311 green</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="88" customHeight="1">
       <c r="A5" s="5" t="n">
@@ -724,8 +751,17 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr"/>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>APPROVE FOR BUILD 47 — given verbally, 2026-07-30 ("Approve all 25")</t>
+        </is>
+      </c>
       <c r="I5" s="5" t="inlineStr"/>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>BUILT 2026-07-30 — pinned; suite 1,311 green</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="88" customHeight="1">
       <c r="A6" s="5" t="n">
@@ -761,8 +797,17 @@
           <t>TINY</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>APPROVE FOR BUILD 47 — given verbally, 2026-07-30 ("Approve all 25")</t>
+        </is>
+      </c>
       <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="9" t="inlineStr">
+        <is>
+          <t>BUILT 2026-07-30 — pinned; suite 1,311 green</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="88" customHeight="1">
       <c r="A7" s="5" t="n">
@@ -798,8 +843,17 @@
           <t>TINY — approved style</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr"/>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>APPROVE FOR BUILD 47 — given verbally, 2026-07-30 ("Approve all 25")</t>
+        </is>
+      </c>
       <c r="I7" s="5" t="inlineStr"/>
+      <c r="J7" s="9" t="inlineStr">
+        <is>
+          <t>BUILT 2026-07-30 — pinned; suite 1,311 green</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -842,8 +896,17 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr"/>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>APPROVE FOR BUILD 47 — given verbally, 2026-07-30 ("Approve all 25")</t>
+        </is>
+      </c>
       <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="9" t="inlineStr">
+        <is>
+          <t>BUILT 2026-07-30 — pinned; suite 1,311 green</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="88" customHeight="1">
       <c r="A10" s="5" t="n">
@@ -879,8 +942,17 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr"/>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>APPROVE FOR BUILD 47 — given verbally, 2026-07-30 ("Approve all 25")</t>
+        </is>
+      </c>
       <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="9" t="inlineStr">
+        <is>
+          <t>BUILT 2026-07-30 — pinned; suite 1,311 green</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="88" customHeight="1">
       <c r="A11" s="5" t="n">
@@ -916,8 +988,17 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr"/>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>APPROVE FOR BUILD 47 — given verbally, 2026-07-30 ("Approve all 25")</t>
+        </is>
+      </c>
       <c r="I11" s="5" t="inlineStr"/>
+      <c r="J11" s="9" t="inlineStr">
+        <is>
+          <t>BUILT 2026-07-30 — pinned; suite 1,311 green</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="88" customHeight="1">
       <c r="A12" s="5" t="n">
@@ -953,8 +1034,17 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr"/>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>APPROVE FOR BUILD 47 — given verbally, 2026-07-30 ("Approve all 25")</t>
+        </is>
+      </c>
       <c r="I12" s="5" t="inlineStr"/>
+      <c r="J12" s="9" t="inlineStr">
+        <is>
+          <t>BUILT 2026-07-30 — pinned; suite 1,311 green</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="88" customHeight="1">
       <c r="A13" s="5" t="n">
@@ -990,8 +1080,17 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr"/>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>APPROVE FOR BUILD 47 — given verbally, 2026-07-30 ("Approve all 25")</t>
+        </is>
+      </c>
       <c r="I13" s="5" t="inlineStr"/>
+      <c r="J13" s="9" t="inlineStr">
+        <is>
+          <t>BUILT 2026-07-30 — pinned; suite 1,311 green</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="88" customHeight="1">
       <c r="A14" s="5" t="n">
@@ -1027,8 +1126,17 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H14" s="5" t="inlineStr"/>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>APPROVE FOR BUILD 47 — given verbally, 2026-07-30 ("Approve all 25")</t>
+        </is>
+      </c>
       <c r="I14" s="5" t="inlineStr"/>
+      <c r="J14" s="9" t="inlineStr">
+        <is>
+          <t>BUILT 2026-07-30 — pinned; suite 1,311 green</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
@@ -1071,8 +1179,17 @@
           <t>TINY — approved element</t>
         </is>
       </c>
-      <c r="H16" s="5" t="inlineStr"/>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>APPROVE FOR BUILD 47 — given verbally, 2026-07-30 ("Approve all 25")</t>
+        </is>
+      </c>
       <c r="I16" s="5" t="inlineStr"/>
+      <c r="J16" s="9" t="inlineStr">
+        <is>
+          <t>BUILT 2026-07-30 — pinned; suite 1,311 green</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="88" customHeight="1">
       <c r="A17" s="5" t="n">
@@ -1108,8 +1225,17 @@
           <t>NO new drawing</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr"/>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>APPROVE FOR BUILD 47 — given verbally, 2026-07-30 ("Approve all 25")</t>
+        </is>
+      </c>
       <c r="I17" s="5" t="inlineStr"/>
+      <c r="J17" s="9" t="inlineStr">
+        <is>
+          <t>BUILT 2026-07-30 — pinned; suite 1,311 green</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="88" customHeight="1">
       <c r="A18" s="5" t="n">
@@ -1145,8 +1271,17 @@
           <t>TINY — words only</t>
         </is>
       </c>
-      <c r="H18" s="5" t="inlineStr"/>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>APPROVE FOR BUILD 47 — given verbally, 2026-07-30 ("Approve all 25")</t>
+        </is>
+      </c>
       <c r="I18" s="5" t="inlineStr"/>
+      <c r="J18" s="9" t="inlineStr">
+        <is>
+          <t>BUILT 2026-07-30 — pinned; suite 1,311 green</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="88" customHeight="1">
       <c r="A19" s="5" t="n">
@@ -1182,8 +1317,17 @@
           <t>TINY — conforming elements</t>
         </is>
       </c>
-      <c r="H19" s="5" t="inlineStr"/>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>APPROVE FOR BUILD 47 — given verbally, 2026-07-30 ("Approve all 25")</t>
+        </is>
+      </c>
       <c r="I19" s="5" t="inlineStr"/>
+      <c r="J19" s="9" t="inlineStr">
+        <is>
+          <t>BUILT 2026-07-30 — pinned; suite 1,311 green</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="88" customHeight="1">
       <c r="A20" s="5" t="n">
@@ -1219,8 +1363,17 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H20" s="5" t="inlineStr"/>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>APPROVE FOR BUILD 47 — given verbally, 2026-07-30 ("Approve all 25")</t>
+        </is>
+      </c>
       <c r="I20" s="5" t="inlineStr"/>
+      <c r="J20" s="9" t="inlineStr">
+        <is>
+          <t>BUILT 2026-07-30 — pinned; suite 1,311 green</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="88" customHeight="1">
       <c r="A21" s="5" t="n">
@@ -1256,8 +1409,17 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H21" s="5" t="inlineStr"/>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>APPROVE FOR BUILD 47 — given verbally, 2026-07-30 ("Approve all 25")</t>
+        </is>
+      </c>
       <c r="I21" s="5" t="inlineStr"/>
+      <c r="J21" s="9" t="inlineStr">
+        <is>
+          <t>BUILT 2026-07-30 — pinned; suite 1,311 green</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="88" customHeight="1">
       <c r="A22" s="5" t="n">
@@ -1293,8 +1455,17 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H22" s="5" t="inlineStr"/>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>APPROVE FOR BUILD 47 — given verbally, 2026-07-30 ("Approve all 25")</t>
+        </is>
+      </c>
       <c r="I22" s="5" t="inlineStr"/>
+      <c r="J22" s="9" t="inlineStr">
+        <is>
+          <t>BUILT 2026-07-30 — pinned; suite 1,311 green</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="88" customHeight="1">
       <c r="A23" s="5" t="n">
@@ -1330,8 +1501,17 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H23" s="5" t="inlineStr"/>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>APPROVE FOR BUILD 47 — given verbally, 2026-07-30 ("Approve all 25")</t>
+        </is>
+      </c>
       <c r="I23" s="5" t="inlineStr"/>
+      <c r="J23" s="9" t="inlineStr">
+        <is>
+          <t>BUILT 2026-07-30 — pinned; suite 1,311 green</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
@@ -1374,8 +1554,17 @@
           <t>NO — only for users who asked</t>
         </is>
       </c>
-      <c r="H25" s="5" t="inlineStr"/>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>APPROVE FOR BUILD 47 — given verbally, 2026-07-30 ("Approve all 25")</t>
+        </is>
+      </c>
       <c r="I25" s="5" t="inlineStr"/>
+      <c r="J25" s="9" t="inlineStr">
+        <is>
+          <t>BUILT 2026-07-30 — pinned; suite 1,311 green</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="88" customHeight="1">
       <c r="A26" s="5" t="n">
@@ -1411,8 +1600,17 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H26" s="5" t="inlineStr"/>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>APPROVE FOR BUILD 47 — given verbally, 2026-07-30 ("Approve all 25")</t>
+        </is>
+      </c>
       <c r="I26" s="5" t="inlineStr"/>
+      <c r="J26" s="9" t="inlineStr">
+        <is>
+          <t>BUILT 2026-07-30 — pinned; suite 1,311 green</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="88" customHeight="1">
       <c r="A27" s="5" t="n">
@@ -1448,8 +1646,17 @@
           <t>NO — approved naming, applied</t>
         </is>
       </c>
-      <c r="H27" s="5" t="inlineStr"/>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>APPROVE FOR BUILD 47 — given verbally, 2026-07-30 ("Approve all 25")</t>
+        </is>
+      </c>
       <c r="I27" s="5" t="inlineStr"/>
+      <c r="J27" s="9" t="inlineStr">
+        <is>
+          <t>BUILT 2026-07-30 — pinned; suite 1,311 green</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="80" customHeight="1">
       <c r="A28" s="5" t="n">
@@ -1485,8 +1692,17 @@
           <t>NO — a standard dialog</t>
         </is>
       </c>
-      <c r="H28" s="5" t="inlineStr"/>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>APPROVE FOR BUILD 47 — given verbally, 2026-07-30 ("Approve all 25")</t>
+        </is>
+      </c>
       <c r="I28" s="5" t="inlineStr"/>
+      <c r="J28" s="9" t="inlineStr">
+        <is>
+          <t>BUILT 2026-07-30 — pinned; suite 1,311 green</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="88" customHeight="1">
       <c r="A29" s="5" t="n">
@@ -1522,8 +1738,17 @@
           <t>TINY — words + one link</t>
         </is>
       </c>
-      <c r="H29" s="5" t="inlineStr"/>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>APPROVE FOR BUILD 47 — given verbally, 2026-07-30 ("Approve all 25")</t>
+        </is>
+      </c>
       <c r="I29" s="5" t="inlineStr"/>
+      <c r="J29" s="9" t="inlineStr">
+        <is>
+          <t>BUILT 2026-07-30 — pinned; suite 1,311 green</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="88" customHeight="1">
       <c r="A30" s="5" t="n">
@@ -1559,8 +1784,17 @@
           <t>TINY — an add row, existing pattern</t>
         </is>
       </c>
-      <c r="H30" s="5" t="inlineStr"/>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>APPROVE FOR BUILD 47 — given verbally, 2026-07-30 ("Approve all 25")</t>
+        </is>
+      </c>
       <c r="I30" s="5" t="inlineStr"/>
+      <c r="J30" s="9" t="inlineStr">
+        <is>
+          <t>BUILT 2026-07-30 — pinned; suite 1,311 green</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">
